--- a/public/crawlability-klompus-september-2026.xlsx
+++ b/public/crawlability-klompus-september-2026.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של klompus ב-SE Ranking (הסריקה האחרונה: 2026-07-20).</t>
+          <t>להריץ מחדש את ה-Website Audit של klompus ב-SE Ranking (הסריקה האחרונה: 2026-07-20); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-klompus-september-2026.xlsx
+++ b/public/crawlability-klompus-september-2026.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של klompus ב-SE Ranking (הסריקה האחרונה: 2026-07-20); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של klompus ב-SE Ranking; הסריקה האחרונה: 2026-07-20.</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-klompus-september-2026.xlsx
+++ b/public/crawlability-klompus-september-2026.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -49,16 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E3E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -82,14 +71,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -481,157 +464,12 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של klompus ב-SE Ranking; הסריקה האחרונה: 2026-07-20.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בסריקה 23.09</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בבדיקה חיה 27.09</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>יעד סופי / יעד להפניה</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>קפיצות</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>קישורים נכנסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>עמודי מקור (עד 10)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>סוג</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה נדרשת</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>יעד מומלץ להפניית 301</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>https://klompus.co.il/</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>403</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>https://klompus.co.il/
-https://klompus.co.il/menu/
-https://klompus.co.il/about/
-https://klompus.co.il/הצהרת-נגישות/</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>חסימות סורק שאומתו כתקינות</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>בסריקה מ-23.09 הסורק הוגבל (קוד 403); בבדיקה חוזרת ב-27.09.2026 העמוד תקין (200). לא נדרש טיפול בעמוד; מומלץ להגדיר חריגה לסורקי SEO ב-WAF.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -697,7 +535,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/sitemap_index.xml</t>
         </is>
@@ -751,7 +589,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/sitemap_index.xml</t>
         </is>
@@ -773,7 +611,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/page-sitemap.xml</t>
         </is>
@@ -795,7 +633,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/sitemap.xml</t>
         </is>
@@ -817,7 +655,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/wp-sitemap.xml</t>
         </is>
@@ -839,7 +677,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/post-sitemap.xml</t>
         </is>
@@ -883,7 +721,7 @@
           <t>קוד 403 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/</t>
         </is>
@@ -896,7 +734,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/</t>
         </is>
@@ -906,7 +744,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (0 הפניות)</t>
         </is>
@@ -918,7 +756,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>http://klompus.co.il/</t>
         </is>
@@ -928,7 +766,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (1 הפניות)</t>
         </is>
@@ -940,7 +778,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>https://www.klompus.co.il/</t>
         </is>
@@ -950,7 +788,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (1 הפניות)</t>
         </is>
@@ -962,7 +800,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>http://www.klompus.co.il/</t>
         </is>
@@ -972,7 +810,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (2 הפניות)</t>
         </is>
@@ -1025,7 +863,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>https://klompus.co.il/</t>
         </is>
@@ -1037,7 +875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-klompus-september-2026.xlsx
+++ b/public/crawlability-klompus-september-2026.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,12 +68,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -439,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -461,6 +469,21 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>פעולה</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>לסרוק מחדש את האתר (הסריקה מ-23.09 נעצרה בעמוד הבית עם 403).</t>
         </is>
       </c>
     </row>
@@ -535,7 +558,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/sitemap_index.xml</t>
         </is>
@@ -589,7 +612,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/sitemap_index.xml</t>
         </is>
@@ -611,7 +634,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/page-sitemap.xml</t>
         </is>
@@ -633,7 +656,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/sitemap.xml</t>
         </is>
@@ -655,7 +678,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/wp-sitemap.xml</t>
         </is>
@@ -677,7 +700,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/post-sitemap.xml</t>
         </is>
@@ -721,7 +744,7 @@
           <t>קוד 403 (סריקה 23.09)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/</t>
         </is>
@@ -734,7 +757,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/</t>
         </is>
@@ -744,7 +767,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (0 הפניות)</t>
         </is>
@@ -756,7 +779,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>http://klompus.co.il/</t>
         </is>
@@ -766,7 +789,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (1 הפניות)</t>
         </is>
@@ -778,7 +801,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>https://www.klompus.co.il/</t>
         </is>
@@ -788,7 +811,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (1 הפניות)</t>
         </is>
@@ -800,7 +823,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>http://www.klompus.co.il/</t>
         </is>
@@ -810,7 +833,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/ (2 הפניות)</t>
         </is>
@@ -863,7 +886,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>https://klompus.co.il/</t>
         </is>
